--- a/burke/keys/CW Darth Maul Rat Diet Genotype.xlsx
+++ b/burke/keys/CW Darth Maul Rat Diet Genotype.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CoryM\UFL Dropbox\Cory Watson\General Lab Resources\Morris Water Maze Data\APoE4 Darth Maul CW 2023\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livejohnshopkins-my.sharepoint.com/personal/abranch6_jh_edu/Documents/Desktop/code/IDCARD/IDCARD/burke/keys/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96FE4FAE-F21F-4684-B3F3-09C510F4E551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{96FE4FAE-F21F-4684-B3F3-09C510F4E551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DCC9FF3-7BE5-48DD-A444-03F34B8763A0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{60BCD71C-80CA-4617-B930-1650DF2FC7DC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{60BCD71C-80CA-4617-B930-1650DF2FC7DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,10 +44,10 @@
     <t>Mash</t>
   </si>
   <si>
-    <t>Wt</t>
+    <t>Keto</t>
   </si>
   <si>
-    <t>Keto</t>
+    <t>WT</t>
   </si>
 </sst>
 </file>
@@ -516,7 +516,7 @@
         <v>1838</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>1</v>
@@ -527,7 +527,7 @@
         <v>1839</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>1</v>
@@ -538,7 +538,7 @@
         <v>1840</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>1</v>
@@ -549,7 +549,7 @@
         <v>1841</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>1</v>
@@ -563,7 +563,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -585,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -596,7 +596,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -607,7 +607,7 @@
         <v>0</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -626,10 +626,10 @@
         <v>1842</v>
       </c>
       <c r="B17" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -637,10 +637,10 @@
         <v>1843</v>
       </c>
       <c r="B18" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -648,10 +648,10 @@
         <v>1844</v>
       </c>
       <c r="B19" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -659,10 +659,10 @@
         <v>1845</v>
       </c>
       <c r="B20" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
